--- a/backend/sample_bachelor_projects.xlsx
+++ b/backend/sample_bachelor_projects.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,147 +415,49 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AI Pioneers</v>
+        <v>Team Alpha</v>
       </c>
       <c r="B2" t="str">
-        <v>AI-Based Student Performance Prediction System</v>
+        <v>AI-Powered Smart Farming Assistant for Nepali Agriculture</v>
       </c>
       <c r="C2" t="str">
-        <v>Aarav Khadka, Binita Shrestha</v>
+        <v>Ram Khadka,Sita Poudel,Gopal Thapa</v>
       </c>
       <c r="D2" t="str">
-        <v>CSE001, CSE002</v>
+        <v>078BCT021,078BCT022,078BCT023</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cloud Ninjas</v>
+        <v>CodeCraft</v>
       </c>
       <c r="B3" t="str">
-        <v>Multi-Cloud Resource Optimization Dashboard</v>
+        <v>E-Hospital: Blockchain-based Medical Record System</v>
       </c>
       <c r="C3" t="str">
-        <v>Chandra Thapa, Deepa Poudel</v>
+        <v>Anita Shrestha,Bibek Sharma,Radha Neupane</v>
       </c>
       <c r="D3" t="str">
-        <v>CSE003, CSE004</v>
+        <v>078BCT031,078BCT032,078BCT033</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Data Warriors</v>
+        <v>CyberNepal</v>
       </c>
       <c r="B4" t="str">
-        <v>Real-Time Analytics for IoT Sensor Networks</v>
+        <v>Network Intrusion Detection for Government Infrastructure</v>
       </c>
       <c r="C4" t="str">
-        <v>Ekaraj Rana, Falguni Neupane</v>
+        <v>Dipendra Karki,Muna Acharya,Rajan Puri</v>
       </c>
       <c r="D4" t="str">
-        <v>CSE005, CSE006</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>EduTech</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Adaptive Learning Platform with AI Tutor</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Ganesh Bhandari, Hima Acharya</v>
-      </c>
-      <c r="D5" t="str">
-        <v>CSE007, CSE008</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>FinSecure</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Blockchain-Based Secure Transaction System</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Indra Joshi, Janaki Dahal</v>
-      </c>
-      <c r="D6" t="str">
-        <v>CSE009, CSE010</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>GreenCompute</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Energy-Efficient Computing Framework</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Krishna Pokharel, Laxmi Regmi</v>
-      </c>
-      <c r="D7" t="str">
-        <v>CSE011, CSE012</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>HealthLink</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Telemedicine Appointment &amp; Record System</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Madhav Bastola, Nisha Lama</v>
-      </c>
-      <c r="D8" t="str">
-        <v>CSE013, CSE014</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>SearchMasters</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Semantic Search Engine for Research Papers</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Om Pandey, Pooja Magar</v>
-      </c>
-      <c r="D9" t="str">
-        <v>CSE015, CSE016</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>CyberShield</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Network Intrusion Detection System</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Rabi Koirala, Sita Bhattarai</v>
-      </c>
-      <c r="D10" t="str">
-        <v>CSE017, CSE018</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>AgriTech</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Smart Agriculture Monitoring with IoT</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Tika Adhikari, Usha Dhami</v>
-      </c>
-      <c r="D11" t="str">
-        <v>CSE019, CSE020</v>
+        <v>080BCT011,080BCT012,080BCT013</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D4"/>
   </ignoredErrors>
 </worksheet>
 </file>